--- a/tools/excel_export/excel/battle_constants.xlsx
+++ b/tools/excel_export/excel/battle_constants.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="140">
   <si>
     <t>key</t>
   </si>
@@ -425,6 +425,12 @@
   </si>
   <si>
     <t>技能槽解锁等级（数组）</t>
+  </si>
+  <si>
+    <t>pxPerMeter</t>
+  </si>
+  <si>
+    <t>1 米 = 多少像素（距离换算口径：设计稿/文案里的 m × 本值 = 配表像素，用于击退/牵引等位移）</t>
   </si>
 </sst>
 </file>
@@ -864,12 +870,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28.5" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1444,6 +1450,17 @@
         <v>137</v>
       </c>
     </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/tools/excel_export/excel/battle_constants.xlsx
+++ b/tools/excel_export/excel/battle_constants.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="150">
   <si>
     <t>key</t>
   </si>
@@ -235,10 +235,46 @@
     <t>英雄升级经验系数</t>
   </si>
   <si>
+    <t>heroUnlockCostBase</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>英雄解锁·金币基准价（英雄列表里**序号最靠前**的那位；默认解锁的英雄不消耗）</t>
+  </si>
+  <si>
+    <t>heroUnlockCostGrowth</t>
+  </si>
+  <si>
+    <t>1.35</t>
+  </si>
+  <si>
+    <t>英雄解锁·每靠后一位的涨价系数（按 units.json 英雄条目 id 升序的序号：价 = 基准 × 系数^序号）</t>
+  </si>
+  <si>
+    <t>heroLevelUpGoldBase</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>英雄升级（Lv.1→2）所需金币</t>
+  </si>
+  <si>
+    <t>heroLevelUpGoldRatio</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>英雄升级·每级涨价系数（Lv.N→N+1 消耗 = 基数 × 系数^(N-1)）</t>
+  </si>
+  <si>
     <t>playerExpFormulaBase</t>
   </si>
   <si>
-    <t>玩家升级经验基数</t>
+    <t>玩家升级经验基数（⚠ 等级经验现在以 player_levels 等级表为准，本值只在等级表不可用时回落）</t>
   </si>
   <si>
     <t>playerExpFormulaRatio</t>
@@ -247,7 +283,7 @@
     <t>1.15</t>
   </si>
   <si>
-    <t>玩家升级经验系数</t>
+    <t>玩家升级经验系数（⚠ 同上：等级表不可用时的回落值）</t>
   </si>
   <si>
     <t>battleExpFormulaBase</t>
@@ -262,9 +298,6 @@
     <t>battleExpFormulaRatio</t>
   </si>
   <si>
-    <t>1.18</t>
-  </si>
-  <si>
     <t>局内升级经验系数</t>
   </si>
   <si>
@@ -280,10 +313,7 @@
     <t>clearRewardPlayerExpBase</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>通关奖励·玩家经验基数</t>
+    <t>通关奖励·玩家经验基数（⚠ 已无消费方：奖励改为「完成任务发放」，见 tasks.json）</t>
   </si>
   <si>
     <t>clearRewardHeroExpBase</t>
@@ -292,7 +322,7 @@
     <t>80</t>
   </si>
   <si>
-    <t>通关奖励·英雄经验基数</t>
+    <t>通关奖励·英雄经验基数（⚠ 已无消费方：奖励改为「完成任务发放」，见 tasks.json）</t>
   </si>
   <si>
     <t>enemyDropExpDefault</t>
@@ -313,7 +343,7 @@
     <t>rewardTimeBasePerSec</t>
   </si>
   <si>
-    <t>0.00067</t>
+    <t>0.00036</t>
   </si>
   <si>
     <t>时间通胀系数（每秒）</t>
@@ -406,7 +436,7 @@
     <t>phaseDefaultRemainingTime</t>
   </si>
   <si>
-    <t>360</t>
+    <t>240</t>
   </si>
   <si>
     <t>阶段默认剩余时间（秒）</t>
@@ -870,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28.5" customWidth="1"/>
@@ -1180,51 +1210,51 @@
         <v>74</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>87</v>
@@ -1257,18 +1287,18 @@
         <v>94</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>98</v>
@@ -1279,18 +1309,18 @@
         <v>99</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>103</v>
@@ -1301,40 +1331,40 @@
         <v>104</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>113</v>
@@ -1345,7 +1375,7 @@
         <v>114</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>115</v>
@@ -1356,18 +1386,18 @@
         <v>116</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>120</v>
@@ -1378,51 +1408,51 @@
         <v>121</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>132</v>
@@ -1433,7 +1463,7 @@
         <v>133</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>134</v>
@@ -1455,10 +1485,54 @@
         <v>138</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>139</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel_export/excel/battle_constants.xlsx
+++ b/tools/excel_export/excel/battle_constants.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="179">
   <si>
     <t>key</t>
   </si>
@@ -461,6 +461,93 @@
   </si>
   <si>
     <t>1 米 = 多少像素（距离换算口径：设计稿/文案里的 m × 本值 = 配表像素，用于击退/牵引等位移）</t>
+  </si>
+  <si>
+    <t>reviveAdPerRun</t>
+  </si>
+  <si>
+    <t>局内·**每局**「看广告复活」的次数上限（0 = 关掉这一条：英雄阵亡时只认背包里的局内复活券；复活券本身能用几次由背包存量决定，不受本键约束）</t>
+  </si>
+  <si>
+    <t>outerDrawCostBase</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>局外遗物抽取·当天第一次抽取的价格（金币；每天 0 点重置回本值）</t>
+  </si>
+  <si>
+    <t>outerDrawCostStep</t>
+  </si>
+  <si>
+    <t>局外遗物抽取·每付费抽一次涨多少（当天第 N 抽 = 基数 + 步长 × (N-1)，付费才涨；抽券不涨）</t>
+  </si>
+  <si>
+    <t>outerDrawCostCap</t>
+  </si>
+  <si>
+    <t>局外遗物抽取·当天单抽价格封顶（0 = 不封顶；十连 = 接下来 10 抽价格逐个累加）</t>
+  </si>
+  <si>
+    <t>shopAdDailyTotalLimit</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>局外商城·每日广告总次数上限（跨商品共用一本账，界面底部「今日广告 N/14」）</t>
+  </si>
+  <si>
+    <t>shopAdCardNeedWatches</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>局外商城·免广告卡需要累计观看的广告次数（攒满即可领；= 每日上限 × 期望天数）</t>
+  </si>
+  <si>
+    <t>shopAdCardHours</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>局外商城·免广告卡生效时长（小时；生效期间局内那两个广告位不再拉起广告）</t>
+  </si>
+  <si>
+    <t>shopStreakMuls</t>
+  </si>
+  <si>
+    <t>[1,1,1.5,1.5,1.5,1.5,2]</t>
+  </si>
+  <si>
+    <t>局外商城·每日补给的连续登录加成（**下标 = 连续天数 - 1**：`[1,1,1.5,1.5,1.5,1.5,2]` = 1~2 天 ×1 / 3~6 天 ×1.5 / ≥7 天 ×2；超出长度按最后一项）</t>
+  </si>
+  <si>
+    <t>shopStreakGiftDay</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>局外商城·每日补给在连续登录达到该天数时额外送券（0 = 不送）</t>
+  </si>
+  <si>
+    <t>shopStreakGiftTickets</t>
+  </si>
+  <si>
+    <t>局外商城·上面那条额外送的本局增益券张数</t>
+  </si>
+  <si>
+    <t>shopBoostTicketValues</t>
+  </si>
+  <si>
+    <t>{"run_start_gold":50,"shop_option_plus":1,"shop_draw_discount":10,"ad_free_draw":1,"kill_buff_discount":10,"gold_gain_bonus":5,"battle_exp_bonus":5,"hero_start_level":1,"hero_select_free":1,"relic_start_gift":1}</t>
+  </si>
+  <si>
+    <t>局外商城·**本局增益券**（A5）每种效果一张券给多少：`{"run_start_gold":50,…}`，键 = `achievements.effect_code` 的 10 个候选取值之一，值 = **一张券折算的效果数值**（百分比类填百分数，如 10 = 10%）；券的合计仍受 `AchievementEffectMeta` 的 `cap` 约束（已达 cap 的效果不再发券）</t>
   </si>
 </sst>
 </file>
@@ -900,12 +987,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28.5" customWidth="1"/>
-    <col min="2" max="2" width="21.5" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="2" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1535,6 +1621,127 @@
         <v>149</v>
       </c>
     </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/tools/excel_export/excel/battle_constants.xlsx
+++ b/tools/excel_export/excel/battle_constants.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="207">
   <si>
     <t>key</t>
   </si>
@@ -301,93 +301,87 @@
     <t>局内升级经验系数</t>
   </si>
   <si>
-    <t>battleLevelMax</t>
+    <t>clearRewardPlayerExpBase</t>
+  </si>
+  <si>
+    <t>通关奖励·玩家经验基数（⚠ 已无消费方：奖励改为「完成任务发放」，见 tasks.json）</t>
+  </si>
+  <si>
+    <t>clearRewardHeroExpBase</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>**一局结算·通用英雄经验基数**（键名里的 clear 是历史读法：2026-11 起它不是"通关才发"那个数，而是「阶段 × 时间」加权后的**满额**。口径真源 = assets/scripts/game/common/RunClearHeroExp.ts 的文件头；通关约等于满额 ⇒ 80 与旧口径"通关固定 80"逐字相同）</t>
+  </si>
+  <si>
+    <t>enemyDropExpDefault</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>怪物掉落经验默认值</t>
+  </si>
+  <si>
+    <t>enemyDropGoldDefault</t>
+  </si>
+  <si>
+    <t>怪物掉落金币默认值</t>
+  </si>
+  <si>
+    <t>rewardTimeBasePerSec</t>
+  </si>
+  <si>
+    <t>0.00036</t>
+  </si>
+  <si>
+    <t>时间通胀系数（每秒）</t>
+  </si>
+  <si>
+    <t>rewardTimeCap</t>
+  </si>
+  <si>
+    <t>时间通胀上限</t>
+  </si>
+  <si>
+    <t>rewardBossGoldBonus</t>
+  </si>
+  <si>
+    <t>经济BOSS·金币加成</t>
+  </si>
+  <si>
+    <t>rewardBossExpBonus</t>
+  </si>
+  <si>
+    <t>经济BOSS·经验加成</t>
+  </si>
+  <si>
+    <t>projectileSpeedDefault</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>弹道默认速度（像素/秒）</t>
+  </si>
+  <si>
+    <t>projectileMaxDistDefault</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>弹道默认最大距离（像素）</t>
+  </si>
+  <si>
+    <t>collisionDetectThreshold</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>局内等级上限</t>
-  </si>
-  <si>
-    <t>clearRewardPlayerExpBase</t>
-  </si>
-  <si>
-    <t>通关奖励·玩家经验基数（⚠ 已无消费方：奖励改为「完成任务发放」，见 tasks.json）</t>
-  </si>
-  <si>
-    <t>clearRewardHeroExpBase</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>通关奖励·英雄经验基数（⚠ 已无消费方：奖励改为「完成任务发放」，见 tasks.json）</t>
-  </si>
-  <si>
-    <t>enemyDropExpDefault</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>怪物掉落经验默认值</t>
-  </si>
-  <si>
-    <t>enemyDropGoldDefault</t>
-  </si>
-  <si>
-    <t>怪物掉落金币默认值</t>
-  </si>
-  <si>
-    <t>rewardTimeBasePerSec</t>
-  </si>
-  <si>
-    <t>0.00036</t>
-  </si>
-  <si>
-    <t>时间通胀系数（每秒）</t>
-  </si>
-  <si>
-    <t>rewardTimeCap</t>
-  </si>
-  <si>
-    <t>时间通胀上限</t>
-  </si>
-  <si>
-    <t>rewardBossGoldBonus</t>
-  </si>
-  <si>
-    <t>经济BOSS·金币加成</t>
-  </si>
-  <si>
-    <t>rewardBossExpBonus</t>
-  </si>
-  <si>
-    <t>经济BOSS·经验加成</t>
-  </si>
-  <si>
-    <t>projectileSpeedDefault</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>弹道默认速度（像素/秒）</t>
-  </si>
-  <si>
-    <t>projectileMaxDistDefault</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>弹道默认最大距离（像素）</t>
-  </si>
-  <si>
-    <t>collisionDetectThreshold</t>
-  </si>
-  <si>
     <t>碰撞检测阈值</t>
   </si>
   <si>
@@ -490,6 +484,96 @@
     <t>局外遗物抽取·当天单抽价格封顶（0 = 不封顶；十连 = 接下来 10 抽价格逐个累加）</t>
   </si>
   <si>
+    <t>runClearGoldBase</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>一局打完发的局外金币·**第 1 局**的曲线值（口径真源 = `assets/scripts/game/common/RunClearReward.ts` 的文件头；只算"真正打完一局"，中途退出不发）</t>
+  </si>
+  <si>
+    <t>runClearGoldDecay</t>
+  </si>
+  <si>
+    <t>一局打完发的局外金币·**每往后一局的衰减系数**（0.6 = 每局只剩 60%；到 floor 就停）</t>
+  </si>
+  <si>
+    <t>runClearGoldFloor</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>一局打完发的局外金币·曲线下限（衰减到这里不再降 —— 这就是"头几局高、后面很少"的那个"很少"）</t>
+  </si>
+  <si>
+    <t>runClearGoldStageDivisor</t>
+  </si>
+  <si>
+    <t>一局打完发的局外金币·完成系数分母（到达第几阶段算打满；3 = 阶段 1/2/3+ 分别给 1/3、2/3、满额。用来堵"反复开局送死刷金币"）</t>
+  </si>
+  <si>
+    <t>runHeroExpWeightStage</t>
+  </si>
+  <si>
+    <t>**一局结算·英雄经验**·阶段维度的权重（现 0.6；与下一行之和 = 1。口径真源 = assets/scripts/game/common/RunClearHeroExp.ts 的文件头，**胜负都发**、不是只有通关）</t>
+  </si>
+  <si>
+    <t>runHeroExpWeightTime</t>
+  </si>
+  <si>
+    <t>一局结算·英雄经验·**时间维度**的权重（现 0.4；两个维度是**相加**不是相乘 —— 打得快与打得久各自都能换经验）</t>
+  </si>
+  <si>
+    <t>runHeroExpStageFull</t>
+  </si>
+  <si>
+    <t>一局结算·英雄经验·阶段**打满**的档位（现 5 = 打到 Boss 阶段就满；阶段进度 = 到达阶段 ÷ 本值，夹 0~1）</t>
+  </si>
+  <si>
+    <t>runHeroExpTimeFull</t>
+  </si>
+  <si>
+    <t>一局结算·英雄经验·时间**打满**的秒数（现 600 = 存活 10 分钟就满；时间进度 = 存活秒数 ÷ 本值，夹 0~1）</t>
+  </si>
+  <si>
+    <t>runHeroExpMin</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>一局结算·英雄经验·**保底下限**（现 8：真正打完一局就有，准备期阵亡也给；这一对上下限就是用户口径「给一个范围」）</t>
+  </si>
+  <si>
+    <t>runHeroExpMax</t>
+  </si>
+  <si>
+    <t>1600</t>
+  </si>
+  <si>
+    <t>一局结算·英雄经验·**单局上限**（现 1600；难度 100 档满额 ≈ 80 × 17.96 ≈ 1437，所以正常玩法够不到封顶，它只兜底配表被调歪）</t>
+  </si>
+  <si>
+    <t>settleAdMulMin</t>
+  </si>
+  <si>
+    <t>结算面板「看广告翻倍」·**倍率下限**（现 1.0；倍率在面板弹出时就掷好并画在按钮上，配 1.0 表示允许出现"这一档没赚头"，见 common/RewardAdBonus 口径 ①）</t>
+  </si>
+  <si>
+    <t>settleAdMulMax</t>
+  </si>
+  <si>
+    <t>结算面板「看广告翻倍」·**倍率上限**（现 3.0；用户口径「看广告给 1~3 倍的奖励」）</t>
+  </si>
+  <si>
+    <t>settleAdMulDecimals</t>
+  </si>
+  <si>
+    <t>结算面板「看广告翻倍」·**小数位数**（现 1 = 用户口径「可以有一位小数」；倍率按档位掷，保证掷出来的数逐字节等于显示的「×2.3」）</t>
+  </si>
+  <si>
     <t>shopAdDailyTotalLimit</t>
   </si>
   <si>
@@ -544,10 +628,10 @@
     <t>shopBoostTicketValues</t>
   </si>
   <si>
-    <t>{"run_start_gold":50,"shop_option_plus":1,"shop_draw_discount":10,"ad_free_draw":1,"kill_buff_discount":10,"gold_gain_bonus":5,"battle_exp_bonus":5,"hero_start_level":1,"hero_select_free":1,"relic_start_gift":1}</t>
-  </si>
-  <si>
-    <t>局外商城·**本局增益券**（A5）每种效果一张券给多少：`{"run_start_gold":50,…}`，键 = `achievements.effect_code` 的 10 个候选取值之一，值 = **一张券折算的效果数值**（百分比类填百分数，如 10 = 10%）；券的合计仍受 `AchievementEffectMeta` 的 `cap` 约束（已达 cap 的效果不再发券）</t>
+    <t>{"run_start_gold":50,"run_start_kill_points":10,"shop_option_plus":1,"shop_draw_discount":10,"ad_free_draw":1,"kill_buff_discount":10,"gold_gain_bonus":5,"battle_exp_bonus":5,"hero_start_level":1,"hero_select_free":1,"relic_start_gift":1}</t>
+  </si>
+  <si>
+    <t>局外商城·**本局增益券**（A5）每种效果一张券给多少：`{"run_start_gold":50,…}`，键 = `achievements.effect_code` 的 11 个候选取值之一（2026-11 起含 `run_start_kill_points`），值 = **一张券折算的效果数值**（百分比类填百分数，如 10 = 10%）；券的合计仍受 `AchievementEffectMeta` 的 `cap` 约束（已达 cap 的效果不再发券）</t>
   </si>
 </sst>
 </file>
@@ -987,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28.5" customWidth="1"/>
@@ -1384,18 +1468,18 @@
         <v>96</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>100</v>
@@ -1417,18 +1501,18 @@
         <v>104</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>108</v>
@@ -1439,40 +1523,40 @@
         <v>109</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>117</v>
@@ -1505,18 +1589,18 @@
         <v>124</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>127</v>
+        <v>12</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>128</v>
@@ -1527,7 +1611,7 @@
         <v>129</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>130</v>
@@ -1538,7 +1622,7 @@
         <v>131</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>132</v>
@@ -1549,18 +1633,18 @@
         <v>133</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>137</v>
@@ -1571,18 +1655,18 @@
         <v>138</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>142</v>
@@ -1593,18 +1677,18 @@
         <v>143</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>53</v>
+        <v>144</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>147</v>
@@ -1615,7 +1699,7 @@
         <v>148</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>149</v>
@@ -1626,18 +1710,18 @@
         <v>150</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>154</v>
@@ -1648,7 +1732,7 @@
         <v>155</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>156</v>
@@ -1659,18 +1743,18 @@
         <v>157</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>161</v>
@@ -1692,54 +1776,186 @@
         <v>165</v>
       </c>
       <c r="B64" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B69" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="C69" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C68" s="4" t="s">
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
         <v>178</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
